--- a/ids720_specific/class_schedule_720_xlsx.xlsx
+++ b/ids720_specific/class_schedule_720_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids720_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24F4DD5-1FE7-444B-A2DA-127A8F9295A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F2B361-5D06-0546-9303-EDB07CB70109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,12 +66,6 @@
 - Jupyter</t>
   </si>
   <si>
-    <t>- `Advanced Command Line &lt;../notebooks/PDS_not_yet_in_coursera/10_commandline/commandline_part2.html&gt;`_
-- `Python packages &lt;../notebooks/class_2/week_4/30_managing_python_packages.html&gt;`_
-- **SETUP 4:** `Jupyter in VS Code &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_in_vscode.html&gt;`_
-- **OPTIONAL SETUP:** `R Jupyter Notebooks &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_r_notebooks.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Ex 1 &lt;../exercises/exercise_CommandLine_2_Advanced.html&gt;`_
 - `Ex 2 &lt;../exercises/exercise_jupytervscode.html&gt;`_</t>
   </si>
@@ -416,6 +410,13 @@
 - **SETUP 2:** `Installing and Configuring VS Code &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_vscode.html&gt;`_
 - `chatGPT and You &lt;../notebooks/PDS_not_yet_in_coursera/99_advice/llms.html&gt;`_
 - `Submit Name Recording and Photos &lt;https://forms.gle/LwATk65tzATHd1JT7&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Advanced Command Line &lt;../notebooks/PDS_not_yet_in_coursera/10_commandline/commandline_part2.html&gt;`_
+- `Python packages &lt;../notebooks/class_2/week_4/30_managing_python_packages.html&gt;`_
+- `conda environments &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_conda_envs.html&gt;`_
+- **SETUP 4:** `Jupyter in VS Code &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_in_vscode.html&gt;`_
+- **OPTIONAL SETUP:** `R Jupyter Notebooks &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_r_notebooks.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -852,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" s="8"/>
     </row>
@@ -878,323 +879,323 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="272" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="109" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
         <v>59</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="15" t="s">
         <v>67</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
         <v>95</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/ids720_specific/class_schedule_720_xlsx.xlsx
+++ b/ids720_specific/class_schedule_720_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids720_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F2B361-5D06-0546-9303-EDB07CB70109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50C2E63-29CE-9E41-A40E-2BF4A8155C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
 - `Visualize Git Branches &lt;https://learngitbranching.js.org/&gt;`_</t>
   </si>
   <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_git.html&gt;`_</t>
-  </si>
-  <si>
     <t>Thurs, Sep 10</t>
   </si>
   <si>
@@ -116,10 +113,6 @@
 - Under the numpy heading, also read everything under `Subsetting Vectors &lt;../notebooks/class_2/week_2/10_why_numpy.html&gt;`_
 - `Numbers in Computers &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/ints_and_floats.html&gt;`_
 - `Writing Good Notebooks &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/writing_good_jupyter_notebooks.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_git_2.html&gt;`_
-- `Ex 2 &lt;../exercises/exercise_numpy_vectors.html&gt;`_</t>
   </si>
   <si>
     <t>Tues, Sep 15</t>
@@ -417,6 +410,14 @@
 - `conda environments &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_conda_envs.html&gt;`_
 - **SETUP 4:** `Jupyter in VS Code &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_in_vscode.html&gt;`_
 - **OPTIONAL SETUP:** `R Jupyter Notebooks &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/jupyter_r_notebooks.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Ex 1 &lt;../exercises/exercise_git_prs.html&gt;`_
+- `Ex 2 &lt;../exercises/exercise_numpy_vectors.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Ex 1 &lt;../exercises/exercise_git.html&gt;`_
+'- `Ex 2 &lt;../exercises/exercise_git_conflicts.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -853,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="8"/>
     </row>
@@ -879,7 +880,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>12</v>
@@ -910,292 +911,292 @@
         <v>19</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="8" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="272" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="109" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="D13" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="15" t="s">
         <v>65</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="D20" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="D24" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
